--- a/R_analysis/output/tables/Tabela_Clusters_HH_Persistentes.xlsx
+++ b/R_analysis/output/tables/Tabela_Clusters_HH_Persistentes.xlsx
@@ -382,7 +382,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -397,7 +397,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -412,7 +412,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -427,7 +427,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -442,7 +442,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -457,7 +457,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>No</t>
         </is>
       </c>
     </row>
